--- a/Empaques/Listado de Oferentes -  Rueda de Negocios de Impresión y Packaging.xlsx
+++ b/Empaques/Listado de Oferentes -  Rueda de Negocios de Impresión y Packaging.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2025_DigiLivo\GERENTE DE PROYECTOS\Proyecto Choriboni\Base Total_Choriboni Parrilla\Sucursarl_Choriboni\Empaques\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521E0639-BC71-4109-8518-A89B280C76AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DA3BEC-0F65-4868-9F6A-8208097F5918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-2070" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,58 +36,125 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Evento: Rueda de Negocios de Impresión y Packaging,</t>
   </si>
   <si>
-    <t>Carlos Pico - Profesional, Películas Flexográficas SAS</t>
-  </si>
-  <si>
-    <t>Catalina Caro Chaves - Director, Ctres Publicidad</t>
-  </si>
-  <si>
-    <t>Andres Cortes Orjuela - Gerente, Soiplast SAS</t>
-  </si>
-  <si>
-    <t>Maria Fernanda Vidal Melo - Gerente, CGRAFIC SAS</t>
-  </si>
-  <si>
-    <t>Angela Patricia Parra Hernández - Director, Offset Gráfico Editores S.A.</t>
-  </si>
-  <si>
-    <t>Jose Oliberto Caviedes - Director, IMPRESOS JC SAS</t>
-  </si>
-  <si>
-    <t>Hugo Rodriguez - Gerente, DOCULISTEN</t>
-  </si>
-  <si>
-    <t>Laura Patiño Bustos - Gerente, Proemflex S.A.S.</t>
-  </si>
-  <si>
-    <t>Natalia Torres - Jefe, ALL 4PACK SAS</t>
-  </si>
-  <si>
-    <t>Karen Julieth Galindo Ruiz - Gerente, Termy Plast JK SAS</t>
-  </si>
-  <si>
-    <t>Diana Monroy - Profesional, edgar devia garcia</t>
-  </si>
-  <si>
-    <t>Diana Paola Madrid Sanchez - Director, CODIFICACION &amp; ETIQUETADO S. A</t>
-  </si>
-  <si>
-    <t>Julian Camilo Cortazar Ponce De Leon - Otro, Servipres Soluciones Empresariales Sas</t>
+    <t xml:space="preserve">Carlos Pico </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Profesional, Películas Flexográficas SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalina Caro Chaves </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Director, Ctres Publicidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andres Cortes Orjuela </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gerente, Soiplast SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria Fernanda Vidal Melo </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gerente, CGRAFIC SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angela Patricia Parra Hernández </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Director, Offset Gráfico Editores S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jose Oliberto Caviedes </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Director, IMPRESOS JC SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Rodriguez </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gerente, DOCULISTEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laura Patiño Bustos </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gerente, Proemflex S.A.S.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natalia Torres </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jefe, ALL 4PACK SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karen Julieth Galindo Ruiz </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gerente, Termy Plast JK SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diana Monroy </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Profesional, edgar devia garcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diana Paola Madrid Sanchez </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Director, CODIFICACION &amp; ETIQUETADO S. A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julian Camilo Cortazar Ponce De Leon </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Otro, Servipres Soluciones Empresariales Sas</t>
+  </si>
+  <si>
+    <t>CODITEQ</t>
+  </si>
+  <si>
+    <t>Erika Hernandez</t>
+  </si>
+  <si>
+    <t>erika.hernandez@coditeq</t>
+  </si>
+  <si>
+    <t>https://coditeq.com.co/#soluciones</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -110,13 +177,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -395,86 +466,147 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:B15"/>
+  <dimension ref="B1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.42578125" customWidth="1"/>
-    <col min="2" max="2" width="76.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.5703125" customWidth="1"/>
-    <col min="4" max="4" width="78.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
+    <row r="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>13</v>
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16">
+        <v>3174380387</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D16" r:id="rId1" xr:uid="{81C0A9FB-7852-4C97-9264-6161A92CA691}"/>
+    <hyperlink ref="F16" r:id="rId2" location="soluciones" xr:uid="{5430A17F-A264-4BD5-809F-3E1B39957702}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>